--- a/refs/heads/main/StructureDefinition-CondicionLE2.xlsx
+++ b/refs/heads/main/StructureDefinition-CondicionLE2.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-CondicionLE2.xlsx
+++ b/refs/heads/main/StructureDefinition-CondicionLE2.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="416">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -919,6 +919,9 @@
     <t>Condition.code.coding.code</t>
   </si>
   <si>
+    <t>http://minsal.cl/listaespera/ValueSet/VSIndicecomorbilidad</t>
+  </si>
+  <si>
     <t>Condition.code.coding.display</t>
   </si>
   <si>
@@ -962,7 +965,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PacienteLE)
 </t>
   </si>
   <si>
@@ -1647,7 +1650,7 @@
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="85.23828125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="50.7109375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.77734375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3905,7 +3908,7 @@
       </c>
       <c r="D20" s="2"/>
       <c r="E20" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>84</v>
@@ -4258,7 +4261,7 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>84</v>
@@ -5430,7 +5433,7 @@
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>84</v>
@@ -5716,13 +5719,11 @@
         <v>74</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="X35" s="2"/>
       <c r="Y35" t="s" s="2">
-        <v>74</v>
+        <v>289</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>74</v>
@@ -5775,7 +5776,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5783,7 +5784,7 @@
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>84</v>
@@ -5892,7 +5893,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6011,7 +6012,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6130,7 +6131,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6156,13 +6157,13 @@
         <v>151</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
@@ -6191,10 +6192,10 @@
         <v>272</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>74</v>
@@ -6212,7 +6213,7 @@
         <v>74</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>75</v>
@@ -6230,28 +6231,28 @@
         <v>74</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6270,17 +6271,17 @@
         <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>74</v>
@@ -6329,7 +6330,7 @@
         <v>74</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>84</v>
@@ -6344,19 +6345,19 @@
         <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>74</v>
@@ -6364,7 +6365,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6387,16 +6388,16 @@
         <v>85</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
@@ -6446,7 +6447,7 @@
         <v>74</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>75</v>
@@ -6461,19 +6462,19 @@
         <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>74</v>
@@ -6481,7 +6482,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6504,16 +6505,16 @@
         <v>85</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6563,7 +6564,7 @@
         <v>74</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>75</v>
@@ -6578,19 +6579,19 @@
         <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>74</v>
@@ -6598,7 +6599,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6621,16 +6622,16 @@
         <v>74</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -6680,7 +6681,7 @@
         <v>74</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>75</v>
@@ -6689,7 +6690,7 @@
         <v>84</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>96</v>
@@ -6704,10 +6705,10 @@
         <v>74</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>74</v>
@@ -6715,7 +6716,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6738,13 +6739,13 @@
         <v>85</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -6795,7 +6796,7 @@
         <v>74</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>75</v>
@@ -6816,13 +6817,13 @@
         <v>74</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>74</v>
@@ -6830,7 +6831,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6853,13 +6854,13 @@
         <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -6910,7 +6911,7 @@
         <v>74</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>75</v>
@@ -6934,10 +6935,10 @@
         <v>74</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>74</v>
@@ -6945,7 +6946,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6968,13 +6969,13 @@
         <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -7025,7 +7026,7 @@
         <v>74</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>75</v>
@@ -7046,13 +7047,13 @@
         <v>74</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>74</v>
@@ -7060,7 +7061,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7083,13 +7084,13 @@
         <v>74</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7140,7 +7141,7 @@
         <v>74</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>75</v>
@@ -7152,7 +7153,7 @@
         <v>74</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>74</v>
@@ -7164,7 +7165,7 @@
         <v>74</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>74</v>
@@ -7175,7 +7176,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7290,7 +7291,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7407,11 +7408,11 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7433,10 +7434,10 @@
         <v>130</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>133</v>
@@ -7491,7 +7492,7 @@
         <v>74</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>75</v>
@@ -7526,7 +7527,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7552,10 +7553,10 @@
         <v>151</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -7585,10 +7586,10 @@
         <v>272</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>74</v>
@@ -7606,7 +7607,7 @@
         <v>74</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>75</v>
@@ -7615,7 +7616,7 @@
         <v>84</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>96</v>
@@ -7624,7 +7625,7 @@
         <v>74</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>161</v>
@@ -7641,7 +7642,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7664,13 +7665,13 @@
         <v>74</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -7721,7 +7722,7 @@
         <v>74</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>75</v>
@@ -7730,7 +7731,7 @@
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>96</v>
@@ -7745,7 +7746,7 @@
         <v>74</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>74</v>
@@ -7756,7 +7757,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -7782,10 +7783,10 @@
         <v>151</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -7815,10 +7816,10 @@
         <v>272</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>74</v>
@@ -7836,7 +7837,7 @@
         <v>74</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>75</v>
@@ -7860,7 +7861,7 @@
         <v>74</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>74</v>
@@ -7871,7 +7872,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7894,16 +7895,16 @@
         <v>74</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -7953,7 +7954,7 @@
         <v>74</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>75</v>
@@ -7965,7 +7966,7 @@
         <v>74</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>74</v>
@@ -7977,7 +7978,7 @@
         <v>74</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>74</v>
@@ -7988,7 +7989,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8103,7 +8104,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8220,11 +8221,11 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8246,10 +8247,10 @@
         <v>130</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>133</v>
@@ -8304,7 +8305,7 @@
         <v>74</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>75</v>
@@ -8339,7 +8340,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8365,10 +8366,10 @@
         <v>151</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -8398,10 +8399,10 @@
         <v>272</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>74</v>
@@ -8419,7 +8420,7 @@
         <v>74</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>75</v>
@@ -8428,13 +8429,13 @@
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>181</v>
@@ -8443,10 +8444,10 @@
         <v>74</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>74</v>
@@ -8454,7 +8455,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8477,13 +8478,13 @@
         <v>85</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8534,7 +8535,7 @@
         <v>74</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>75</v>
@@ -8543,7 +8544,7 @@
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>96</v>
@@ -8558,10 +8559,10 @@
         <v>74</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>74</v>
@@ -8569,7 +8570,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8592,13 +8593,13 @@
         <v>74</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -8649,7 +8650,7 @@
         <v>74</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>75</v>
@@ -8664,16 +8665,16 @@
         <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>74</v>
